--- a/STM32U5_BOM.xlsx
+++ b/STM32U5_BOM.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,14 +32,14 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00666666"/>
+      <color rgb="002F5496"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -52,11 +52,21 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +77,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -100,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,14 +137,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -496,73 +526,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STM32U5 Posture Monitor Watch BOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>STM32U5 姿态异常监护手环 — 硬件物料清单 (BOM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NUCLEO-U575ZI-Q | STM32U575ZIT6Q Cortex-M33 160MHz 2MB/786KB</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
+          <t>基于 NUCLEO-U575ZI-Q | 主控 STM32U575ZIT6Q Cortex-M33 160MHz | 优先立创商城 (LCSC) 可购</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>器件名称</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Model / Spec</t>
+          <t>型号/规格</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Qty</t>
+          <t>数量</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>单位</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>立创编号</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>单价(约)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>用途说明</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>购买备注</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1. MCU &amp; Debug</t>
+          <t>一、主控板（非立创渠道）</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -571,14 +613,16 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>NUCLEO Dev Board</t>
+          <t>NUCLEO 开发板</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -589,648 +633,988 @@
       <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>MCU + STLINK-V3E + Arduino/Morpho I/O</t>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>块</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>ST official, STM32U575ZIT6Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="n">
+          <t>¥190</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>主控板，载 STM32U575ZIT6Q + STLINK-V3E 调试器</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>淘宝/得捷/Mouser 购买，立创不售官方开发板</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>二、传感器模块</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Micro-USB Cable</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>USB-A to Micro-USB</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>六轴陀螺仪加速度计模块</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>GY-521 (MPU6050)</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Power + STLINK debug/flash</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Included with NUCLEO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2. Sensors</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>C24112</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>¥8</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>加速度 + 陀螺仪 6 轴数据采集，I2C 通信</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>搜索"MPU6050模块 GY-521"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>6-Axis IMU Module</t>
+          <t>三轴磁力计模块 (可选)</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>GY-521 (MPU6050)</t>
+          <t>GY-273 (HMC5883L)</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Accel + Gyro data acquisition</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>C19871</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>I2C, 3.3V, addr 0x68</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="n">
+          <t>¥6</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>地磁传感器，修正 yaw 漂移</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>AHRS_USE_MAG=0 时可不买</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>三、告警输出</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Magnetometer (optional)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>GY-273 (HMC5883L)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>微型振动马达</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>1027 扁平偏心轮电机</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Yaw drift correction</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>I2C, skip if AHRS_USE_MAG=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>3. Alert Output</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>C2895556</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>跌倒/倾斜触觉告警，PWM 调速</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>需配 NPN 三极管驱动 (如 S8050 C2146)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Vibration Motor Module</t>
+          <t>NPN 三极管</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1027 Eccentric Motor</t>
+          <t>S8050 (TO-92)</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>C2146</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>¥0.2</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>驱动振动马达</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>直插 RGB LED 共阴</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>5mm 共阴三色 LED</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Fall/tilt haptic alert</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>PWM, built-in NPN driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>RGB LED Module</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>5mm Common Cathode</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Status: green/yellow/red</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>GPIO, 220R series each</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>C965027</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>¥1</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>状态指示: 绿(正常) 黄(倾斜) 红(跌倒)</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>需 3 颗 220Ω 限流电阻</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Buzzer Module (optional)</t>
+          <t>直插电阻 220Ω</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3.3V Active Buzzer</t>
+          <t>1/4W ±5% 碳膜</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>C17405</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>¥0.1</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>RGB LED 限流</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>有源蜂鸣器模块 (可选)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>3.3V 有源蜂鸣器</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Audio alert</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>GPIO or PWM</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>4. Input</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Tactile Switch Module</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>6x6mm Push Button</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>C31955</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>声音告警辅助</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>搜索"3.3V有源蜂鸣器模块"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>四、输入交互</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>轻触开关 6x6mm</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>6x6x5mm 四脚轻触</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Long-press cancel alarm + spare</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Pull-up input, debounced</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>5. Power</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Li-Po Battery</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>3.7V 500-1000mAh</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Wearable standalone power</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>&lt; 50x30mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="8" t="n">
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>C31892</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>¥0.3</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>长按解除告警 + 预留功能按键</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>配 10kΩ 上拉电阻</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>LDO Regulator Module</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>AMS1117-3.3V</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Battery 3.7V -&gt; stable 3.3V</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Or use NUCLEO Vin pin</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>直插电阻 10kΩ</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>1/4W ±5% 碳膜</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>C17408</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>¥0.1</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>按键上拉</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>五、电源系统</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Battery Charger Module</t>
+          <t>AMS1117-3.3V 稳压模块</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>TP4056</t>
+          <t>AMS1117-3.3 降压模块</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Li-Po charge management</t>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>C6186</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Micro-USB input, protection IC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>6. Wiring &amp; Fixture</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="n">
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>电池 3.7V → 3.3V 稳定供电</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>或直接用 NUCLEO Vin 引脚 (5V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Dupont Wire F-M</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>20cm Female-Male 2.54mm</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>TP4056 锂电池充电模块</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>TP4056 Type-C 充电板</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>NUCLEO pin -&gt; modules</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>10 pcs/set</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="6" t="n">
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>C382139</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>锂电池充电管理，含过充过放保护</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>搜索"TP4056充电模块 Type-C"</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Dupont Wire M-M</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>20cm Male-Male 2.54mm</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>锂聚合物电池</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>3.7V 800mAh 502535</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Breadboard jumpers</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>10 pcs/set</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="8" t="n">
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>块</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>¥15</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>可穿戴独立供电</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>淘宝购买，立创不售电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>六、连接与固定</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Mini Breadboard</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>830 Tie-points</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>杜邦线 母对母 20cm</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>2.54mm 1P-1P 20cm</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>pcs</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Module prototyping</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>165x55mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>排</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>C895920</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>传感器模块 ↔ NUCLEO 引脚连接</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>10根/排</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Cable Ties</t>
+          <t>杜邦线 公对公 20cm</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>3x100mm Black</t>
+          <t>2.54mm 1P-1P 20cm</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>pack</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Fix battery &amp; modules to board</t>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>排</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>C895919</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>~20 pcs</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="8" t="n">
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>面包板内跳线</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>10根/排</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Heat Shrink Tubing</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>phi3mm + phi5mm</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>830 孔面包板</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>830 孔 Mini 面包板 165x55mm</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>pack</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Solder joint insulation</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>20cm each</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Key Parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>MCU: STM32U575ZIT6Q, Cortex-M33 + FPv5-SP-D16, 160MHz, 2MB Flash / 786KB SRAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>IMU: accel +/-8g / gyro +/-2000dps, ODR 200Hz, I2C 400kHz Fast Mode</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>AHRS: Mahony filter, 100Hz, magnetometer optional (AHRS_USE_MAG compile switch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Power target: STOP mode uA-level, IMU INT + RTC wakeup</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Build: arm-none-eabi-gcc + Makefile -&gt; build/stm32u5_skeleton.{elf,bin,hex}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>NUCLEO pins: LED=PC7, BTN=PC13, UART2=PA2(TX)/PA3(RX), I2C1=PB8(SCL)/PB9(SDA)</t>
-        </is>
-      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>块</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>C124363</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>¥8</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>模块临时搭接验证</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>尼龙扎带 3x100mm</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>3x100mm 黑色</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>包</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>C306488</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>¥5</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>固定电池和模块到开发板</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>100根/包</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>热缩管套装</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>φ1.5/3/5mm 混装</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>包</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>C275726</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>¥6</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>焊接接头绝缘</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>费用汇总</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>开发板: ¥190 (淘宝/得捷) | 立创可购物料 (不含电池): ¥56 | 电池: ¥15 (淘宝) | 总计 约 ¥261</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>去掉磁力计和蜂鸣器等可选件: 约 ¥250 即可跑通核心功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>关键参数</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>MCU: STM32U575ZIT6Q | Cortex-M33 + FPv5-SP-D16 | 160MHz | 2MB Flash / 786KB SRAM | LQFP144</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>IMU: 加速度 ±8g / 陀螺仪 ±2000°/s | 采样率 100Hz | I2C 400kHz | 7-bit 地址 0x68</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>AHRS: Mahony 互补滤波器 | 加速度+陀螺仪融合 | 磁力计 yaw 修正可选 (AHRS_USE_MAG=0/1)</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>外设引脚 (NUCLEO): LED=PC7 | 按键=PC13 | USART2=PA2(TX)/PA3(RX) | I2C1=PB8(SCL)/PB9(SDA)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="15" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>跌倒检测: Free-fall (0.6g) → Impact (3g) → Post-impact tilt (&gt;60deg) → 5 帧防抖确认</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="15" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>功耗: STOP 模式目标 &lt; 50μA | IMU 运动中断唤醒 | RTC 定时唤醒 | LPBAM 后台外设</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>编译: arm-none-eabi-gcc + Makefile → build/stm32u5_skeleton.elf/.bin/.hex</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A5:G5"/>
+  <mergeCells count="19">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STM32U5_BOM.xlsx
+++ b/STM32U5_BOM.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -763,7 +763,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>三、告警输出</t>
+          <t>三、通信模块</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -781,12 +781,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>微型振动马达</t>
+          <t>NFC 读写模块</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>1027 扁平偏心轮电机</t>
+          <t>PN532 NFC RFID V3 模块</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
@@ -799,203 +799,203 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
+          <t>C232619</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>¥18</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>13.56MHz NFC 读写/卡模拟，I2C/SPI/UART</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>搜索"PN532模块"，支持 NTAG/NFC Tag/Mifare</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>四、告警输出</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>微型振动马达</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>1027 扁平偏心轮电机</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
           <t>C2895556</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>¥3</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>跌倒/倾斜触觉告警，PWM 调速</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>需配 NPN 三极管驱动 (如 S8050 C2146)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>NPN 三极管</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>S8050 (TO-92)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D14" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>C2146</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>¥0.2</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>驱动振动马达</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>直插 RGB LED 共阴</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>5mm 共阴三色 LED</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>C965027</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>¥1</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>状态指示: 绿(正常) 黄(倾斜) 红(跌倒)</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>需 3 颗 220Ω 限流电阻</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>直插电阻 220Ω</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>1/4W ±5% 碳膜</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D16" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>C17405</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>¥0.1</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>RGB LED 限流</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>有源蜂鸣器模块 (可选)</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>3.3V 有源蜂鸣器</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>C31955</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>¥2</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>声音告警辅助</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>搜索"3.3V有源蜂鸣器模块"</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>四、输入交互</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="10" t="n"/>
+      <c r="I16" s="12" t="inlineStr"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1003,96 +1003,100 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
+          <t>有源蜂鸣器模块 (可选)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>3.3V 有源蜂鸣器</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>C31955</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>声音告警辅助</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>搜索"3.3V有源蜂鸣器模块"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>五、输入交互</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
           <t>轻触开关 6x6mm</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>6x6x5mm 四脚轻触</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>C31892</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>¥0.3</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>长按解除告警 + 预留功能按键</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>配 10kΩ 上拉电阻</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>直插电阻 10kΩ</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>1/4W ±5% 碳膜</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>C17408</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>¥0.1</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>按键上拉</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>五、电源系统</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="n">
@@ -1100,143 +1104,139 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
+          <t>直插电阻 10kΩ</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>1/4W ±5% 碳膜</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>C17408</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>¥0.1</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>按键上拉</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>六、电源系统</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
           <t>AMS1117-3.3V 稳压模块</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>AMS1117-3.3 降压模块</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D22" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>C6186</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>¥2</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>电池 3.7V → 3.3V 稳定供电</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>或直接用 NUCLEO Vin 引脚 (5V)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>TP4056 锂电池充电模块</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>TP4056 Type-C 充电板</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>C382139</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>¥3</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>锂电池充电管理，含过充过放保护</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>搜索"TP4056充电模块 Type-C"</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>锂聚合物电池</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>3.7V 800mAh 502535</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>块</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>¥15</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>可穿戴独立供电</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>淘宝购买，立创不售电池</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>六、连接与固定</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="10" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="11" t="n">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>杜邦线 母对母 20cm</t>
+          <t>锂聚合物电池</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>2.54mm 1P-1P 20cm</t>
+          <t>3.7V 800mAh 502535</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
@@ -1257,257 +1257,285 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
+          <t>块</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>¥15</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>可穿戴独立供电</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>淘宝购买，立创不售电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>七、连接与固定</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>杜邦线 母对母 20cm</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>2.54mm 1P-1P 20cm</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
           <t>排</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>C895920</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>¥3</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>传感器模块 ↔ NUCLEO 引脚连接</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>10根/排</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>杜邦线 公对公 20cm</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>2.54mm 1P-1P 20cm</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D27" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>排</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>C895919</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>¥3</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>面包板内跳线</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>10根/排</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>830 孔面包板</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>830 孔 Mini 面包板 165x55mm</t>
         </is>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>块</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>C124363</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>¥8</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>模块临时搭接验证</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>尼龙扎带 3x100mm</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>3x100mm 黑色</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D29" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>包</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>C306488</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>¥5</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>固定电池和模块到开发板</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>100根/包</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>热缩管套装</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>φ1.5/3/5mm 混装</t>
         </is>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>包</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>C275726</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>¥6</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>焊接接头绝缘</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>费用汇总</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>开发板: ¥190 (淘宝/得捷) | 立创可购物料 (不含电池): ¥56 | 电池: ¥15 (淘宝) | 总计 约 ¥261</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>去掉磁力计和蜂鸣器等可选件: 约 ¥250 即可跑通核心功能</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>开发板: ¥190 (淘宝/得捷) | 立创可购物料 (不含电池): ¥74 | 电池: ¥15 (淘宝) | 总计 约 ¥279</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>去掉磁力计和蜂鸣器等可选件: 约 ¥268 即可跑通核心功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>关键参数</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="15" t="n"/>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="15" t="n"/>
-      <c r="H34" s="15" t="n"/>
-      <c r="I34" s="15" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>MCU: STM32U575ZIT6Q | Cortex-M33 + FPv5-SP-D16 | 160MHz | 2MB Flash / 786KB SRAM | LQFP144</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
-      <c r="G35" s="15" t="n"/>
-      <c r="H35" s="15" t="n"/>
-      <c r="I35" s="15" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>IMU: 加速度 ±8g / 陀螺仪 ±2000°/s | 采样率 100Hz | I2C 400kHz | 7-bit 地址 0x68</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
@@ -1522,7 +1550,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>AHRS: Mahony 互补滤波器 | 加速度+陀螺仪融合 | 磁力计 yaw 修正可选 (AHRS_USE_MAG=0/1)</t>
+          <t>MCU: STM32U575ZIT6Q | Cortex-M33 + FPv5-SP-D16 | 160MHz | 2MB Flash / 786KB SRAM | LQFP144</t>
         </is>
       </c>
       <c r="B37" s="15" t="n"/>
@@ -1537,7 +1565,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>外设引脚 (NUCLEO): LED=PC7 | 按键=PC13 | USART2=PA2(TX)/PA3(RX) | I2C1=PB8(SCL)/PB9(SDA)</t>
+          <t>IMU: 加速度 ±8g / 陀螺仪 ±2000°/s | 采样率 100Hz | I2C 400kHz | 7-bit 地址 0x68</t>
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
@@ -1552,7 +1580,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>跌倒检测: Free-fall (0.6g) → Impact (3g) → Post-impact tilt (&gt;60deg) → 5 帧防抖确认</t>
+          <t>AHRS: Mahony 互补滤波器 | 加速度+陀螺仪融合 | 磁力计 yaw 修正可选 (AHRS_USE_MAG=0/1)</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
@@ -1567,7 +1595,7 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>功耗: STOP 模式目标 &lt; 50μA | IMU 运动中断唤醒 | RTC 定时唤醒 | LPBAM 后台外设</t>
+          <t>外设引脚 (NUCLEO): LED=PC7 | 按键=PC13 | USART2=PA2(TX)/PA3(RX) | I2C1=PB8(SCL)/PB9(SDA)</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
@@ -1582,7 +1610,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>编译: arm-none-eabi-gcc + Makefile → build/stm32u5_skeleton.elf/.bin/.hex</t>
+          <t>跌倒检测: Free-fall (0.6g) → Impact (3g) → Post-impact tilt (&gt;60deg) → 5 帧防抖确认</t>
         </is>
       </c>
       <c r="B41" s="15" t="n"/>
@@ -1594,27 +1622,58 @@
       <c r="H41" s="15" t="n"/>
       <c r="I41" s="15" t="n"/>
     </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>功耗: STOP 模式目标 &lt; 50μA | IMU 运动中断唤醒 | RTC 定时唤醒 | LPBAM 后台外设</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>编译: arm-none-eabi-gcc + Makefile → build/stm32u5_skeleton.elf/.bin/.hex</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A35:I35"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A43:I43"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A30:I30"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/STM32U5_BOM.xlsx
+++ b/STM32U5_BOM.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -818,63 +818,63 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>NFC 标签贴纸</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>NTAG215 空白标签</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>张</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>C2892084</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>¥2</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>NFC 标签，可写入急救信息/设备配置</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>搜索"NTAG215 NFC标签"，13.56MHz 504字节</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>四、告警输出</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>微型振动马达</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>1027 扁平偏心轮电机</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>C2895556</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>¥3</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>跌倒/倾斜触觉告警，PWM 调速</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>需配 NPN 三极管驱动 (如 S8050 C2146)</t>
-        </is>
-      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="11" t="n">
@@ -882,16 +882,16 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>NPN 三极管</t>
+          <t>微型振动马达</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>S8050 (TO-92)</t>
+          <t>1027 扁平偏心轮电机</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -900,20 +900,24 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>C2146</t>
+          <t>C2895556</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>¥0.2</t>
+          <t>¥3</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>驱动振动马达</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr"/>
+          <t>跌倒/倾斜触觉告警，PWM 调速</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>需配 NPN 三极管驱动 (如 S8050 C2146)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -921,16 +925,16 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>直插 RGB LED 共阴</t>
+          <t>NPN 三极管</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>5mm 共阴三色 LED</t>
+          <t>S8050 (TO-92)</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -939,24 +943,20 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>C965027</t>
+          <t>C2146</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>¥1</t>
+          <t>¥0.2</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>状态指示: 绿(正常) 黄(倾斜) 红(跌倒)</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>需 3 颗 220Ω 限流电阻</t>
-        </is>
-      </c>
+          <t>驱动振动马达</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="11" t="n">
@@ -964,16 +964,16 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>直插电阻 220Ω</t>
+          <t>直插 RGB LED 共阴</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>1/4W ±5% 碳膜</t>
+          <t>5mm 共阴三色 LED</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -982,20 +982,24 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>C17405</t>
+          <t>C965027</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>¥0.1</t>
+          <t>¥1</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>RGB LED 限流</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr"/>
+          <t>状态指示: 绿(正常) 黄(倾斜) 红(跌倒)</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>需 3 颗 220Ω 限流电阻</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1003,100 +1007,96 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
+          <t>直插电阻 220Ω</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1/4W ±5% 碳膜</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>C17405</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>¥0.1</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>RGB LED 限流</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
           <t>有源蜂鸣器模块 (可选)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>3.3V 有源蜂鸣器</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D18" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>C31955</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>¥2</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>声音告警辅助</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>搜索"3.3V有源蜂鸣器模块"</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>五、输入交互</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>轻触开关 6x6mm</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>6x6x5mm 四脚轻触</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>C31892</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>¥0.3</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>长按解除告警 + 预留功能按键</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>配 10kΩ 上拉电阻</t>
-        </is>
-      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="n">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>直插电阻 10kΩ</t>
+          <t>轻触开关 6x6mm</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>1/4W ±5% 碳膜</t>
+          <t>6x6x5mm 四脚轻触</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
@@ -1122,78 +1122,78 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
+          <t>C31892</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>¥0.3</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>长按解除告警 + 预留功能按键</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>配 10kΩ 上拉电阻</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>直插电阻 10kΩ</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>1/4W ±5% 碳膜</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
           <t>C17408</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>¥0.1</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>按键上拉</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>六、电源系统</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>AMS1117-3.3V 稳压模块</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>AMS1117-3.3 降压模块</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>C6186</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>¥2</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>电池 3.7V → 3.3V 稳定供电</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>或直接用 NUCLEO Vin 引脚 (5V)</t>
-        </is>
-      </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>TP4056 锂电池充电模块</t>
+          <t>AMS1117-3.3V 稳压模块</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>TP4056 Type-C 充电板</t>
+          <t>AMS1117-3.3 降压模块</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
@@ -1219,22 +1219,22 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>C382139</t>
+          <t>C6186</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>¥3</t>
+          <t>¥2</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>锂电池充电管理，含过充过放保护</t>
+          <t>电池 3.7V → 3.3V 稳定供电</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>搜索"TP4056充电模块 Type-C"</t>
+          <t>或直接用 NUCLEO Vin 引脚 (5V)</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>锂聚合物电池</t>
+          <t>TP4056 锂电池充电模块</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>3.7V 800mAh 502535</t>
+          <t>TP4056 Type-C 充电板</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
@@ -1257,87 +1257,87 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>C382139</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>¥3</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>锂电池充电管理，含过充过放保护</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>搜索"TP4056充电模块 Type-C"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>锂聚合物电池</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>3.7V 800mAh 502535</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
           <t>块</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>¥15</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>可穿戴独立供电</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>淘宝购买，立创不售电池</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>七、连接与固定</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>杜邦线 母对母 20cm</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>2.54mm 1P-1P 20cm</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>排</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>C895920</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>¥3</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>传感器模块 ↔ NUCLEO 引脚连接</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>10根/排</t>
-        </is>
-      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="11" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>杜邦线 公对公 20cm</t>
+          <t>杜邦线 母对母 20cm</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>C895919</t>
+          <t>C895920</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>面包板内跳线</t>
+          <t>传感器模块 ↔ NUCLEO 引脚连接</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>830 孔面包板</t>
+          <t>杜邦线 公对公 20cm</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>830 孔 Mini 面包板 165x55mm</t>
+          <t>2.54mm 1P-1P 20cm</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
@@ -1401,25 +1401,29 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>块</t>
+          <t>排</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>C124363</t>
+          <t>C895919</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>¥8</t>
+          <t>¥3</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>模块临时搭接验证</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr"/>
+          <t>面包板内跳线</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>10根/排</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="11" t="n">
@@ -1427,12 +1431,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>尼龙扎带 3x100mm</t>
+          <t>830 孔面包板</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>3x100mm 黑色</t>
+          <t>830 孔 Mini 面包板 165x55mm</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
@@ -1440,29 +1444,25 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>包</t>
+          <t>块</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>C306488</t>
+          <t>C124363</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>¥5</t>
+          <t>¥8</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>固定电池和模块到开发板</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>100根/包</t>
-        </is>
-      </c>
+          <t>模块临时搭接验证</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="n">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>热缩管套装</t>
+          <t>尼龙扎带 3x100mm</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>φ1.5/3/5mm 混装</t>
+          <t>3x100mm 黑色</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
@@ -1488,69 +1488,97 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
+          <t>C306488</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>¥5</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>固定电池和模块到开发板</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>100根/包</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>热缩管套装</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>φ1.5/3/5mm 混装</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>包</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
           <t>C275726</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>¥6</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>焊接接头绝缘</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>费用汇总</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="15" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>开发板: ¥190 (淘宝/得捷) | 立创可购物料 (不含电池): ¥74 | 电池: ¥15 (淘宝) | 总计 约 ¥279</t>
-        </is>
-      </c>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>去掉磁力计和蜂鸣器等可选件: 约 ¥268 即可跑通核心功能</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+          <t>开发板: ¥190 (淘宝/得捷) | 立创可购物料 (不含电池): ¥84 | 电池: ¥15 (淘宝) | 总计 约 ¥289</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>去掉磁力计和蜂鸣器等可选件: 约 ¥276 即可跑通核心功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>关键参数</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
-      <c r="I36" s="15" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>MCU: STM32U575ZIT6Q | Cortex-M33 + FPv5-SP-D16 | 160MHz | 2MB Flash / 786KB SRAM | LQFP144</t>
         </is>
       </c>
       <c r="B37" s="15" t="n"/>
@@ -1565,7 +1593,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>IMU: 加速度 ±8g / 陀螺仪 ±2000°/s | 采样率 100Hz | I2C 400kHz | 7-bit 地址 0x68</t>
+          <t>MCU: STM32U575ZIT6Q | Cortex-M33 + FPv5-SP-D16 | 160MHz | 2MB Flash / 786KB SRAM | LQFP144</t>
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
@@ -1580,7 +1608,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>AHRS: Mahony 互补滤波器 | 加速度+陀螺仪融合 | 磁力计 yaw 修正可选 (AHRS_USE_MAG=0/1)</t>
+          <t>IMU: 加速度 ±8g / 陀螺仪 ±2000°/s | 采样率 100Hz | I2C 400kHz | 7-bit 地址 0x68</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
@@ -1595,7 +1623,7 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>外设引脚 (NUCLEO): LED=PC7 | 按键=PC13 | USART2=PA2(TX)/PA3(RX) | I2C1=PB8(SCL)/PB9(SDA)</t>
+          <t>AHRS: Mahony 互补滤波器 | 加速度+陀螺仪融合 | 磁力计 yaw 修正可选 (AHRS_USE_MAG=0/1)</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
@@ -1610,7 +1638,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>跌倒检测: Free-fall (0.6g) → Impact (3g) → Post-impact tilt (&gt;60deg) → 5 帧防抖确认</t>
+          <t>外设引脚 (NUCLEO): LED=PC7 | 按键=PC13 | USART2=PA2(TX)/PA3(RX) | I2C1=PB8(SCL)/PB9(SDA)</t>
         </is>
       </c>
       <c r="B41" s="15" t="n"/>
@@ -1625,7 +1653,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>功耗: STOP 模式目标 &lt; 50μA | IMU 运动中断唤醒 | RTC 定时唤醒 | LPBAM 后台外设</t>
+          <t>跌倒检测: Free-fall (0.6g) → Impact (3g) → Post-impact tilt (&gt;60deg) → 5 帧防抖确认</t>
         </is>
       </c>
       <c r="B42" s="15" t="n"/>
@@ -1640,7 +1668,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>编译: arm-none-eabi-gcc + Makefile → build/stm32u5_skeleton.elf/.bin/.hex</t>
+          <t>功耗: STOP 模式目标 &lt; 50μA | IMU 运动中断唤醒 | RTC 定时唤醒 | LPBAM 后台外设</t>
         </is>
       </c>
       <c r="B43" s="15" t="n"/>
@@ -1652,27 +1680,42 @@
       <c r="H43" s="15" t="n"/>
       <c r="I43" s="15" t="n"/>
     </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>编译: arm-none-eabi-gcc + Makefile → build/stm32u5_skeleton.elf/.bin/.hex</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="15" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A44:I44"/>
     <mergeCell ref="A40:I40"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
